--- a/docs/payment-schedule-templates/Payment Schedules - Customer Portal/Collection_Schedule_Template_12mo.xlsx
+++ b/docs/payment-schedule-templates/Payment Schedules - Customer Portal/Collection_Schedule_Template_12mo.xlsx
@@ -947,20 +947,55 @@
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="14">
-      <c r="A2" s="20" t="n"/>
-      <c r="B2" s="20" t="n"/>
-      <c r="C2" s="20" t="n"/>
-      <c r="D2" s="20" t="n"/>
-      <c r="E2" s="20" t="n"/>
-      <c r="F2" s="20" t="n"/>
-      <c r="G2" s="21" t="n"/>
-      <c r="H2" s="21" t="n"/>
-      <c r="I2" s="21" t="n"/>
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>{{########}}</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>Nyandoro</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>+17785808657</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr">
+        <is>
+          <t>alex@michaeltenable.com</t>
+        </is>
+      </c>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>Internal Tester</t>
+        </is>
+      </c>
+      <c r="G2" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I2" s="21" t="n">
+        <v>120000</v>
+      </c>
       <c r="J2" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="K2" s="21" t="n"/>
-      <c r="L2" s="23" t="n"/>
+      <c r="K2" s="21">
+        <f>IF(J2=0,"",ROUND((I2-H2)/J2,2))</f>
+        <v/>
+      </c>
+      <c r="L2" s="23" t="n">
+        <v>46147</v>
+      </c>
       <c r="M2" s="21" t="n"/>
       <c r="N2" s="21" t="n"/>
       <c r="O2" s="21" t="n"/>
@@ -975,15 +1010,15 @@
       <c r="X2" s="21" t="n"/>
       <c r="Y2" s="21" t="n"/>
       <c r="Z2" s="24">
-        <f>SUM(M2:X2)</f>
+        <f>H2+SUM(M2:X2)</f>
         <v/>
       </c>
       <c r="AA2" s="24">
-        <f>I2-Z2</f>
+        <f>I2-H2-SUM(M2:X2)</f>
         <v/>
       </c>
       <c r="AB2" s="25">
-        <f>IF(I2=0,"",Z2/I2)</f>
+        <f>IF(I2=0,"",(H2+SUM(M2:X2))/I2)</f>
         <v/>
       </c>
       <c r="AC2" s="26" t="n"/>
@@ -1024,15 +1059,15 @@
       <c r="X3" s="21" t="n"/>
       <c r="Y3" s="21" t="n"/>
       <c r="Z3" s="24">
-        <f>SUM(M3:X3)</f>
+        <f>H3+SUM(M3:X3)</f>
         <v/>
       </c>
       <c r="AA3" s="24">
-        <f>I3-Z3</f>
+        <f>I3-H3-SUM(M3:X3)</f>
         <v/>
       </c>
       <c r="AB3" s="25">
-        <f>IF(I3=0,"",Z3/I3)</f>
+        <f>IF(I3=0,"",(H3+SUM(M3:X3))/I3)</f>
         <v/>
       </c>
       <c r="AC3" s="26" t="n"/>
@@ -1073,15 +1108,15 @@
       <c r="X4" s="21" t="n"/>
       <c r="Y4" s="21" t="n"/>
       <c r="Z4" s="24">
-        <f>SUM(M4:X4)</f>
+        <f>H4+SUM(M4:X4)</f>
         <v/>
       </c>
       <c r="AA4" s="24">
-        <f>I4-Z4</f>
+        <f>I4-H4-SUM(M4:X4)</f>
         <v/>
       </c>
       <c r="AB4" s="25">
-        <f>IF(I4=0,"",Z4/I4)</f>
+        <f>IF(I4=0,"",(H4+SUM(M4:X4))/I4)</f>
         <v/>
       </c>
       <c r="AC4" s="26" t="n"/>
@@ -1122,15 +1157,15 @@
       <c r="X5" s="21" t="n"/>
       <c r="Y5" s="21" t="n"/>
       <c r="Z5" s="24">
-        <f>SUM(M5:X5)</f>
+        <f>H5+SUM(M5:X5)</f>
         <v/>
       </c>
       <c r="AA5" s="24">
-        <f>I5-Z5</f>
+        <f>I5-H5-SUM(M5:X5)</f>
         <v/>
       </c>
       <c r="AB5" s="25">
-        <f>IF(I5=0,"",Z5/I5)</f>
+        <f>IF(I5=0,"",(H5+SUM(M5:X5))/I5)</f>
         <v/>
       </c>
       <c r="AC5" s="26" t="n"/>
@@ -1171,15 +1206,15 @@
       <c r="X6" s="21" t="n"/>
       <c r="Y6" s="21" t="n"/>
       <c r="Z6" s="24">
-        <f>SUM(M6:X6)</f>
+        <f>H6+SUM(M6:X6)</f>
         <v/>
       </c>
       <c r="AA6" s="24">
-        <f>I6-Z6</f>
+        <f>I6-H6-SUM(M6:X6)</f>
         <v/>
       </c>
       <c r="AB6" s="25">
-        <f>IF(I6=0,"",Z6/I6)</f>
+        <f>IF(I6=0,"",(H6+SUM(M6:X6))/I6)</f>
         <v/>
       </c>
       <c r="AC6" s="26" t="n"/>
@@ -1220,15 +1255,15 @@
       <c r="X7" s="21" t="n"/>
       <c r="Y7" s="21" t="n"/>
       <c r="Z7" s="24">
-        <f>SUM(M7:X7)</f>
+        <f>H7+SUM(M7:X7)</f>
         <v/>
       </c>
       <c r="AA7" s="24">
-        <f>I7-Z7</f>
+        <f>I7-H7-SUM(M7:X7)</f>
         <v/>
       </c>
       <c r="AB7" s="25">
-        <f>IF(I7=0,"",Z7/I7)</f>
+        <f>IF(I7=0,"",(H7+SUM(M7:X7))/I7)</f>
         <v/>
       </c>
       <c r="AC7" s="26" t="n"/>
@@ -1269,15 +1304,15 @@
       <c r="X8" s="21" t="n"/>
       <c r="Y8" s="21" t="n"/>
       <c r="Z8" s="24">
-        <f>SUM(M8:X8)</f>
+        <f>H8+SUM(M8:X8)</f>
         <v/>
       </c>
       <c r="AA8" s="24">
-        <f>I8-Z8</f>
+        <f>I8-H8-SUM(M8:X8)</f>
         <v/>
       </c>
       <c r="AB8" s="25">
-        <f>IF(I8=0,"",Z8/I8)</f>
+        <f>IF(I8=0,"",(H8+SUM(M8:X8))/I8)</f>
         <v/>
       </c>
       <c r="AC8" s="26" t="n"/>
@@ -1318,15 +1353,15 @@
       <c r="X9" s="21" t="n"/>
       <c r="Y9" s="21" t="n"/>
       <c r="Z9" s="24">
-        <f>SUM(M9:X9)</f>
+        <f>H9+SUM(M9:X9)</f>
         <v/>
       </c>
       <c r="AA9" s="24">
-        <f>I9-Z9</f>
+        <f>I9-H9-SUM(M9:X9)</f>
         <v/>
       </c>
       <c r="AB9" s="25">
-        <f>IF(I9=0,"",Z9/I9)</f>
+        <f>IF(I9=0,"",(H9+SUM(M9:X9))/I9)</f>
         <v/>
       </c>
       <c r="AC9" s="26" t="n"/>
@@ -1367,15 +1402,15 @@
       <c r="X10" s="21" t="n"/>
       <c r="Y10" s="21" t="n"/>
       <c r="Z10" s="24">
-        <f>SUM(M10:X10)</f>
+        <f>H10+SUM(M10:X10)</f>
         <v/>
       </c>
       <c r="AA10" s="24">
-        <f>I10-Z10</f>
+        <f>I10-H10-SUM(M10:X10)</f>
         <v/>
       </c>
       <c r="AB10" s="25">
-        <f>IF(I10=0,"",Z10/I10)</f>
+        <f>IF(I10=0,"",(H10+SUM(M10:X10))/I10)</f>
         <v/>
       </c>
       <c r="AC10" s="26" t="n"/>
@@ -1416,15 +1451,15 @@
       <c r="X11" s="21" t="n"/>
       <c r="Y11" s="21" t="n"/>
       <c r="Z11" s="24">
-        <f>SUM(M11:X11)</f>
+        <f>H11+SUM(M11:X11)</f>
         <v/>
       </c>
       <c r="AA11" s="24">
-        <f>I11-Z11</f>
+        <f>I11-H11-SUM(M11:X11)</f>
         <v/>
       </c>
       <c r="AB11" s="25">
-        <f>IF(I11=0,"",Z11/I11)</f>
+        <f>IF(I11=0,"",(H11+SUM(M11:X11))/I11)</f>
         <v/>
       </c>
       <c r="AC11" s="26" t="n"/>
@@ -1465,15 +1500,15 @@
       <c r="X12" s="21" t="n"/>
       <c r="Y12" s="21" t="n"/>
       <c r="Z12" s="24">
-        <f>SUM(M12:X12)</f>
+        <f>H12+SUM(M12:X12)</f>
         <v/>
       </c>
       <c r="AA12" s="24">
-        <f>I12-Z12</f>
+        <f>I12-H12-SUM(M12:X12)</f>
         <v/>
       </c>
       <c r="AB12" s="25">
-        <f>IF(I12=0,"",Z12/I12)</f>
+        <f>IF(I12=0,"",(H12+SUM(M12:X12))/I12)</f>
         <v/>
       </c>
       <c r="AC12" s="26" t="n"/>
@@ -1514,15 +1549,15 @@
       <c r="X13" s="21" t="n"/>
       <c r="Y13" s="21" t="n"/>
       <c r="Z13" s="24">
-        <f>SUM(M13:X13)</f>
+        <f>H13+SUM(M13:X13)</f>
         <v/>
       </c>
       <c r="AA13" s="24">
-        <f>I13-Z13</f>
+        <f>I13-H13-SUM(M13:X13)</f>
         <v/>
       </c>
       <c r="AB13" s="25">
-        <f>IF(I13=0,"",Z13/I13)</f>
+        <f>IF(I13=0,"",(H13+SUM(M13:X13))/I13)</f>
         <v/>
       </c>
       <c r="AC13" s="26" t="n"/>
@@ -1563,15 +1598,15 @@
       <c r="X14" s="21" t="n"/>
       <c r="Y14" s="21" t="n"/>
       <c r="Z14" s="24">
-        <f>SUM(M14:X14)</f>
+        <f>H14+SUM(M14:X14)</f>
         <v/>
       </c>
       <c r="AA14" s="24">
-        <f>I14-Z14</f>
+        <f>I14-H14-SUM(M14:X14)</f>
         <v/>
       </c>
       <c r="AB14" s="25">
-        <f>IF(I14=0,"",Z14/I14)</f>
+        <f>IF(I14=0,"",(H14+SUM(M14:X14))/I14)</f>
         <v/>
       </c>
       <c r="AC14" s="26" t="n"/>
@@ -1612,15 +1647,15 @@
       <c r="X15" s="21" t="n"/>
       <c r="Y15" s="21" t="n"/>
       <c r="Z15" s="24">
-        <f>SUM(M15:X15)</f>
+        <f>H15+SUM(M15:X15)</f>
         <v/>
       </c>
       <c r="AA15" s="24">
-        <f>I15-Z15</f>
+        <f>I15-H15-SUM(M15:X15)</f>
         <v/>
       </c>
       <c r="AB15" s="25">
-        <f>IF(I15=0,"",Z15/I15)</f>
+        <f>IF(I15=0,"",(H15+SUM(M15:X15))/I15)</f>
         <v/>
       </c>
       <c r="AC15" s="26" t="n"/>
@@ -1661,15 +1696,15 @@
       <c r="X16" s="21" t="n"/>
       <c r="Y16" s="21" t="n"/>
       <c r="Z16" s="24">
-        <f>SUM(M16:X16)</f>
+        <f>H16+SUM(M16:X16)</f>
         <v/>
       </c>
       <c r="AA16" s="24">
-        <f>I16-Z16</f>
+        <f>I16-H16-SUM(M16:X16)</f>
         <v/>
       </c>
       <c r="AB16" s="25">
-        <f>IF(I16=0,"",Z16/I16)</f>
+        <f>IF(I16=0,"",(H16+SUM(M16:X16))/I16)</f>
         <v/>
       </c>
       <c r="AC16" s="26" t="n"/>
@@ -1710,15 +1745,15 @@
       <c r="X17" s="21" t="n"/>
       <c r="Y17" s="21" t="n"/>
       <c r="Z17" s="24">
-        <f>SUM(M17:X17)</f>
+        <f>H17+SUM(M17:X17)</f>
         <v/>
       </c>
       <c r="AA17" s="24">
-        <f>I17-Z17</f>
+        <f>I17-H17-SUM(M17:X17)</f>
         <v/>
       </c>
       <c r="AB17" s="25">
-        <f>IF(I17=0,"",Z17/I17)</f>
+        <f>IF(I17=0,"",(H17+SUM(M17:X17))/I17)</f>
         <v/>
       </c>
       <c r="AC17" s="26" t="n"/>
@@ -1759,15 +1794,15 @@
       <c r="X18" s="21" t="n"/>
       <c r="Y18" s="21" t="n"/>
       <c r="Z18" s="24">
-        <f>SUM(M18:X18)</f>
+        <f>H18+SUM(M18:X18)</f>
         <v/>
       </c>
       <c r="AA18" s="24">
-        <f>I18-Z18</f>
+        <f>I18-H18-SUM(M18:X18)</f>
         <v/>
       </c>
       <c r="AB18" s="25">
-        <f>IF(I18=0,"",Z18/I18)</f>
+        <f>IF(I18=0,"",(H18+SUM(M18:X18))/I18)</f>
         <v/>
       </c>
       <c r="AC18" s="26" t="n"/>
@@ -1808,15 +1843,15 @@
       <c r="X19" s="21" t="n"/>
       <c r="Y19" s="21" t="n"/>
       <c r="Z19" s="24">
-        <f>SUM(M19:X19)</f>
+        <f>H19+SUM(M19:X19)</f>
         <v/>
       </c>
       <c r="AA19" s="24">
-        <f>I19-Z19</f>
+        <f>I19-H19-SUM(M19:X19)</f>
         <v/>
       </c>
       <c r="AB19" s="25">
-        <f>IF(I19=0,"",Z19/I19)</f>
+        <f>IF(I19=0,"",(H19+SUM(M19:X19))/I19)</f>
         <v/>
       </c>
       <c r="AC19" s="26" t="n"/>
@@ -1857,15 +1892,15 @@
       <c r="X20" s="21" t="n"/>
       <c r="Y20" s="21" t="n"/>
       <c r="Z20" s="24">
-        <f>SUM(M20:X20)</f>
+        <f>H20+SUM(M20:X20)</f>
         <v/>
       </c>
       <c r="AA20" s="24">
-        <f>I20-Z20</f>
+        <f>I20-H20-SUM(M20:X20)</f>
         <v/>
       </c>
       <c r="AB20" s="25">
-        <f>IF(I20=0,"",Z20/I20)</f>
+        <f>IF(I20=0,"",(H20+SUM(M20:X20))/I20)</f>
         <v/>
       </c>
       <c r="AC20" s="26" t="n"/>
@@ -1906,15 +1941,15 @@
       <c r="X21" s="21" t="n"/>
       <c r="Y21" s="21" t="n"/>
       <c r="Z21" s="24">
-        <f>SUM(M21:X21)</f>
+        <f>H21+SUM(M21:X21)</f>
         <v/>
       </c>
       <c r="AA21" s="24">
-        <f>I21-Z21</f>
+        <f>I21-H21-SUM(M21:X21)</f>
         <v/>
       </c>
       <c r="AB21" s="25">
-        <f>IF(I21=0,"",Z21/I21)</f>
+        <f>IF(I21=0,"",(H21+SUM(M21:X21))/I21)</f>
         <v/>
       </c>
       <c r="AC21" s="26" t="n"/>
@@ -1955,15 +1990,15 @@
       <c r="X22" s="21" t="n"/>
       <c r="Y22" s="21" t="n"/>
       <c r="Z22" s="24">
-        <f>SUM(M22:X22)</f>
+        <f>H22+SUM(M22:X22)</f>
         <v/>
       </c>
       <c r="AA22" s="24">
-        <f>I22-Z22</f>
+        <f>I22-H22-SUM(M22:X22)</f>
         <v/>
       </c>
       <c r="AB22" s="25">
-        <f>IF(I22=0,"",Z22/I22)</f>
+        <f>IF(I22=0,"",(H22+SUM(M22:X22))/I22)</f>
         <v/>
       </c>
       <c r="AC22" s="26" t="n"/>
@@ -2004,15 +2039,15 @@
       <c r="X23" s="21" t="n"/>
       <c r="Y23" s="21" t="n"/>
       <c r="Z23" s="24">
-        <f>SUM(M23:X23)</f>
+        <f>H23+SUM(M23:X23)</f>
         <v/>
       </c>
       <c r="AA23" s="24">
-        <f>I23-Z23</f>
+        <f>I23-H23-SUM(M23:X23)</f>
         <v/>
       </c>
       <c r="AB23" s="25">
-        <f>IF(I23=0,"",Z23/I23)</f>
+        <f>IF(I23=0,"",(H23+SUM(M23:X23))/I23)</f>
         <v/>
       </c>
       <c r="AC23" s="26" t="n"/>
@@ -2053,15 +2088,15 @@
       <c r="X24" s="21" t="n"/>
       <c r="Y24" s="21" t="n"/>
       <c r="Z24" s="24">
-        <f>SUM(M24:X24)</f>
+        <f>H24+SUM(M24:X24)</f>
         <v/>
       </c>
       <c r="AA24" s="24">
-        <f>I24-Z24</f>
+        <f>I24-H24-SUM(M24:X24)</f>
         <v/>
       </c>
       <c r="AB24" s="25">
-        <f>IF(I24=0,"",Z24/I24)</f>
+        <f>IF(I24=0,"",(H24+SUM(M24:X24))/I24)</f>
         <v/>
       </c>
       <c r="AC24" s="26" t="n"/>
@@ -2102,15 +2137,15 @@
       <c r="X25" s="21" t="n"/>
       <c r="Y25" s="21" t="n"/>
       <c r="Z25" s="24">
-        <f>SUM(M25:X25)</f>
+        <f>H25+SUM(M25:X25)</f>
         <v/>
       </c>
       <c r="AA25" s="24">
-        <f>I25-Z25</f>
+        <f>I25-H25-SUM(M25:X25)</f>
         <v/>
       </c>
       <c r="AB25" s="25">
-        <f>IF(I25=0,"",Z25/I25)</f>
+        <f>IF(I25=0,"",(H25+SUM(M25:X25))/I25)</f>
         <v/>
       </c>
       <c r="AC25" s="26" t="n"/>
@@ -2151,15 +2186,15 @@
       <c r="X26" s="21" t="n"/>
       <c r="Y26" s="21" t="n"/>
       <c r="Z26" s="24">
-        <f>SUM(M26:X26)</f>
+        <f>H26+SUM(M26:X26)</f>
         <v/>
       </c>
       <c r="AA26" s="24">
-        <f>I26-Z26</f>
+        <f>I26-H26-SUM(M26:X26)</f>
         <v/>
       </c>
       <c r="AB26" s="25">
-        <f>IF(I26=0,"",Z26/I26)</f>
+        <f>IF(I26=0,"",(H26+SUM(M26:X26))/I26)</f>
         <v/>
       </c>
       <c r="AC26" s="26" t="n"/>
@@ -2200,15 +2235,15 @@
       <c r="X27" s="21" t="n"/>
       <c r="Y27" s="21" t="n"/>
       <c r="Z27" s="24">
-        <f>SUM(M27:X27)</f>
+        <f>H27+SUM(M27:X27)</f>
         <v/>
       </c>
       <c r="AA27" s="24">
-        <f>I27-Z27</f>
+        <f>I27-H27-SUM(M27:X27)</f>
         <v/>
       </c>
       <c r="AB27" s="25">
-        <f>IF(I27=0,"",Z27/I27)</f>
+        <f>IF(I27=0,"",(H27+SUM(M27:X27))/I27)</f>
         <v/>
       </c>
       <c r="AC27" s="26" t="n"/>
@@ -2249,15 +2284,15 @@
       <c r="X28" s="21" t="n"/>
       <c r="Y28" s="21" t="n"/>
       <c r="Z28" s="24">
-        <f>SUM(M28:X28)</f>
+        <f>H28+SUM(M28:X28)</f>
         <v/>
       </c>
       <c r="AA28" s="24">
-        <f>I28-Z28</f>
+        <f>I28-H28-SUM(M28:X28)</f>
         <v/>
       </c>
       <c r="AB28" s="25">
-        <f>IF(I28=0,"",Z28/I28)</f>
+        <f>IF(I28=0,"",(H28+SUM(M28:X28))/I28)</f>
         <v/>
       </c>
       <c r="AC28" s="26" t="n"/>
@@ -2298,15 +2333,15 @@
       <c r="X29" s="21" t="n"/>
       <c r="Y29" s="21" t="n"/>
       <c r="Z29" s="24">
-        <f>SUM(M29:X29)</f>
+        <f>H29+SUM(M29:X29)</f>
         <v/>
       </c>
       <c r="AA29" s="24">
-        <f>I29-Z29</f>
+        <f>I29-H29-SUM(M29:X29)</f>
         <v/>
       </c>
       <c r="AB29" s="25">
-        <f>IF(I29=0,"",Z29/I29)</f>
+        <f>IF(I29=0,"",(H29+SUM(M29:X29))/I29)</f>
         <v/>
       </c>
       <c r="AC29" s="26" t="n"/>
@@ -2347,15 +2382,15 @@
       <c r="X30" s="21" t="n"/>
       <c r="Y30" s="21" t="n"/>
       <c r="Z30" s="24">
-        <f>SUM(M30:X30)</f>
+        <f>H30+SUM(M30:X30)</f>
         <v/>
       </c>
       <c r="AA30" s="24">
-        <f>I30-Z30</f>
+        <f>I30-H30-SUM(M30:X30)</f>
         <v/>
       </c>
       <c r="AB30" s="25">
-        <f>IF(I30=0,"",Z30/I30)</f>
+        <f>IF(I30=0,"",(H30+SUM(M30:X30))/I30)</f>
         <v/>
       </c>
       <c r="AC30" s="26" t="n"/>
@@ -2396,15 +2431,15 @@
       <c r="X31" s="21" t="n"/>
       <c r="Y31" s="21" t="n"/>
       <c r="Z31" s="24">
-        <f>SUM(M31:X31)</f>
+        <f>H31+SUM(M31:X31)</f>
         <v/>
       </c>
       <c r="AA31" s="24">
-        <f>I31-Z31</f>
+        <f>I31-H31-SUM(M31:X31)</f>
         <v/>
       </c>
       <c r="AB31" s="25">
-        <f>IF(I31=0,"",Z31/I31)</f>
+        <f>IF(I31=0,"",(H31+SUM(M31:X31))/I31)</f>
         <v/>
       </c>
       <c r="AC31" s="26" t="n"/>
@@ -2445,15 +2480,15 @@
       <c r="X32" s="21" t="n"/>
       <c r="Y32" s="21" t="n"/>
       <c r="Z32" s="24">
-        <f>SUM(M32:X32)</f>
+        <f>H32+SUM(M32:X32)</f>
         <v/>
       </c>
       <c r="AA32" s="24">
-        <f>I32-Z32</f>
+        <f>I32-H32-SUM(M32:X32)</f>
         <v/>
       </c>
       <c r="AB32" s="25">
-        <f>IF(I32=0,"",Z32/I32)</f>
+        <f>IF(I32=0,"",(H32+SUM(M32:X32))/I32)</f>
         <v/>
       </c>
       <c r="AC32" s="26" t="n"/>
@@ -2494,15 +2529,15 @@
       <c r="X33" s="21" t="n"/>
       <c r="Y33" s="21" t="n"/>
       <c r="Z33" s="24">
-        <f>SUM(M33:X33)</f>
+        <f>H33+SUM(M33:X33)</f>
         <v/>
       </c>
       <c r="AA33" s="24">
-        <f>I33-Z33</f>
+        <f>I33-H33-SUM(M33:X33)</f>
         <v/>
       </c>
       <c r="AB33" s="25">
-        <f>IF(I33=0,"",Z33/I33)</f>
+        <f>IF(I33=0,"",(H33+SUM(M33:X33))/I33)</f>
         <v/>
       </c>
       <c r="AC33" s="26" t="n"/>
@@ -2543,15 +2578,15 @@
       <c r="X34" s="21" t="n"/>
       <c r="Y34" s="21" t="n"/>
       <c r="Z34" s="24">
-        <f>SUM(M34:X34)</f>
+        <f>H34+SUM(M34:X34)</f>
         <v/>
       </c>
       <c r="AA34" s="24">
-        <f>I34-Z34</f>
+        <f>I34-H34-SUM(M34:X34)</f>
         <v/>
       </c>
       <c r="AB34" s="25">
-        <f>IF(I34=0,"",Z34/I34)</f>
+        <f>IF(I34=0,"",(H34+SUM(M34:X34))/I34)</f>
         <v/>
       </c>
       <c r="AC34" s="26" t="n"/>
@@ -2592,15 +2627,15 @@
       <c r="X35" s="21" t="n"/>
       <c r="Y35" s="21" t="n"/>
       <c r="Z35" s="24">
-        <f>SUM(M35:X35)</f>
+        <f>H35+SUM(M35:X35)</f>
         <v/>
       </c>
       <c r="AA35" s="24">
-        <f>I35-Z35</f>
+        <f>I35-H35-SUM(M35:X35)</f>
         <v/>
       </c>
       <c r="AB35" s="25">
-        <f>IF(I35=0,"",Z35/I35)</f>
+        <f>IF(I35=0,"",(H35+SUM(M35:X35))/I35)</f>
         <v/>
       </c>
       <c r="AC35" s="26" t="n"/>
@@ -2641,15 +2676,15 @@
       <c r="X36" s="21" t="n"/>
       <c r="Y36" s="21" t="n"/>
       <c r="Z36" s="24">
-        <f>SUM(M36:X36)</f>
+        <f>H36+SUM(M36:X36)</f>
         <v/>
       </c>
       <c r="AA36" s="24">
-        <f>I36-Z36</f>
+        <f>I36-H36-SUM(M36:X36)</f>
         <v/>
       </c>
       <c r="AB36" s="25">
-        <f>IF(I36=0,"",Z36/I36)</f>
+        <f>IF(I36=0,"",(H36+SUM(M36:X36))/I36)</f>
         <v/>
       </c>
       <c r="AC36" s="26" t="n"/>
@@ -2690,15 +2725,15 @@
       <c r="X37" s="21" t="n"/>
       <c r="Y37" s="21" t="n"/>
       <c r="Z37" s="24">
-        <f>SUM(M37:X37)</f>
+        <f>H37+SUM(M37:X37)</f>
         <v/>
       </c>
       <c r="AA37" s="24">
-        <f>I37-Z37</f>
+        <f>I37-H37-SUM(M37:X37)</f>
         <v/>
       </c>
       <c r="AB37" s="25">
-        <f>IF(I37=0,"",Z37/I37)</f>
+        <f>IF(I37=0,"",(H37+SUM(M37:X37))/I37)</f>
         <v/>
       </c>
       <c r="AC37" s="26" t="n"/>
@@ -2739,15 +2774,15 @@
       <c r="X38" s="21" t="n"/>
       <c r="Y38" s="21" t="n"/>
       <c r="Z38" s="24">
-        <f>SUM(M38:X38)</f>
+        <f>H38+SUM(M38:X38)</f>
         <v/>
       </c>
       <c r="AA38" s="24">
-        <f>I38-Z38</f>
+        <f>I38-H38-SUM(M38:X38)</f>
         <v/>
       </c>
       <c r="AB38" s="25">
-        <f>IF(I38=0,"",Z38/I38)</f>
+        <f>IF(I38=0,"",(H38+SUM(M38:X38))/I38)</f>
         <v/>
       </c>
       <c r="AC38" s="26" t="n"/>
@@ -2788,15 +2823,15 @@
       <c r="X39" s="21" t="n"/>
       <c r="Y39" s="21" t="n"/>
       <c r="Z39" s="24">
-        <f>SUM(M39:X39)</f>
+        <f>H39+SUM(M39:X39)</f>
         <v/>
       </c>
       <c r="AA39" s="24">
-        <f>I39-Z39</f>
+        <f>I39-H39-SUM(M39:X39)</f>
         <v/>
       </c>
       <c r="AB39" s="25">
-        <f>IF(I39=0,"",Z39/I39)</f>
+        <f>IF(I39=0,"",(H39+SUM(M39:X39))/I39)</f>
         <v/>
       </c>
       <c r="AC39" s="26" t="n"/>
@@ -2837,15 +2872,15 @@
       <c r="X40" s="21" t="n"/>
       <c r="Y40" s="21" t="n"/>
       <c r="Z40" s="24">
-        <f>SUM(M40:X40)</f>
+        <f>H40+SUM(M40:X40)</f>
         <v/>
       </c>
       <c r="AA40" s="24">
-        <f>I40-Z40</f>
+        <f>I40-H40-SUM(M40:X40)</f>
         <v/>
       </c>
       <c r="AB40" s="25">
-        <f>IF(I40=0,"",Z40/I40)</f>
+        <f>IF(I40=0,"",(H40+SUM(M40:X40))/I40)</f>
         <v/>
       </c>
       <c r="AC40" s="26" t="n"/>
@@ -2886,15 +2921,15 @@
       <c r="X41" s="21" t="n"/>
       <c r="Y41" s="21" t="n"/>
       <c r="Z41" s="24">
-        <f>SUM(M41:X41)</f>
+        <f>H41+SUM(M41:X41)</f>
         <v/>
       </c>
       <c r="AA41" s="24">
-        <f>I41-Z41</f>
+        <f>I41-H41-SUM(M41:X41)</f>
         <v/>
       </c>
       <c r="AB41" s="25">
-        <f>IF(I41=0,"",Z41/I41)</f>
+        <f>IF(I41=0,"",(H41+SUM(M41:X41))/I41)</f>
         <v/>
       </c>
       <c r="AC41" s="26" t="n"/>
@@ -2935,15 +2970,15 @@
       <c r="X42" s="21" t="n"/>
       <c r="Y42" s="21" t="n"/>
       <c r="Z42" s="24">
-        <f>SUM(M42:X42)</f>
+        <f>H42+SUM(M42:X42)</f>
         <v/>
       </c>
       <c r="AA42" s="24">
-        <f>I42-Z42</f>
+        <f>I42-H42-SUM(M42:X42)</f>
         <v/>
       </c>
       <c r="AB42" s="25">
-        <f>IF(I42=0,"",Z42/I42)</f>
+        <f>IF(I42=0,"",(H42+SUM(M42:X42))/I42)</f>
         <v/>
       </c>
       <c r="AC42" s="26" t="n"/>
@@ -2984,15 +3019,15 @@
       <c r="X43" s="21" t="n"/>
       <c r="Y43" s="21" t="n"/>
       <c r="Z43" s="24">
-        <f>SUM(M43:X43)</f>
+        <f>H43+SUM(M43:X43)</f>
         <v/>
       </c>
       <c r="AA43" s="24">
-        <f>I43-Z43</f>
+        <f>I43-H43-SUM(M43:X43)</f>
         <v/>
       </c>
       <c r="AB43" s="25">
-        <f>IF(I43=0,"",Z43/I43)</f>
+        <f>IF(I43=0,"",(H43+SUM(M43:X43))/I43)</f>
         <v/>
       </c>
       <c r="AC43" s="26" t="n"/>
@@ -3033,15 +3068,15 @@
       <c r="X44" s="21" t="n"/>
       <c r="Y44" s="21" t="n"/>
       <c r="Z44" s="24">
-        <f>SUM(M44:X44)</f>
+        <f>H44+SUM(M44:X44)</f>
         <v/>
       </c>
       <c r="AA44" s="24">
-        <f>I44-Z44</f>
+        <f>I44-H44-SUM(M44:X44)</f>
         <v/>
       </c>
       <c r="AB44" s="25">
-        <f>IF(I44=0,"",Z44/I44)</f>
+        <f>IF(I44=0,"",(H44+SUM(M44:X44))/I44)</f>
         <v/>
       </c>
       <c r="AC44" s="26" t="n"/>
@@ -3082,15 +3117,15 @@
       <c r="X45" s="21" t="n"/>
       <c r="Y45" s="21" t="n"/>
       <c r="Z45" s="24">
-        <f>SUM(M45:X45)</f>
+        <f>H45+SUM(M45:X45)</f>
         <v/>
       </c>
       <c r="AA45" s="24">
-        <f>I45-Z45</f>
+        <f>I45-H45-SUM(M45:X45)</f>
         <v/>
       </c>
       <c r="AB45" s="25">
-        <f>IF(I45=0,"",Z45/I45)</f>
+        <f>IF(I45=0,"",(H45+SUM(M45:X45))/I45)</f>
         <v/>
       </c>
       <c r="AC45" s="26" t="n"/>
@@ -3131,15 +3166,15 @@
       <c r="X46" s="21" t="n"/>
       <c r="Y46" s="21" t="n"/>
       <c r="Z46" s="24">
-        <f>SUM(M46:X46)</f>
+        <f>H46+SUM(M46:X46)</f>
         <v/>
       </c>
       <c r="AA46" s="24">
-        <f>I46-Z46</f>
+        <f>I46-H46-SUM(M46:X46)</f>
         <v/>
       </c>
       <c r="AB46" s="25">
-        <f>IF(I46=0,"",Z46/I46)</f>
+        <f>IF(I46=0,"",(H46+SUM(M46:X46))/I46)</f>
         <v/>
       </c>
       <c r="AC46" s="26" t="n"/>
@@ -3180,15 +3215,15 @@
       <c r="X47" s="21" t="n"/>
       <c r="Y47" s="21" t="n"/>
       <c r="Z47" s="24">
-        <f>SUM(M47:X47)</f>
+        <f>H47+SUM(M47:X47)</f>
         <v/>
       </c>
       <c r="AA47" s="24">
-        <f>I47-Z47</f>
+        <f>I47-H47-SUM(M47:X47)</f>
         <v/>
       </c>
       <c r="AB47" s="25">
-        <f>IF(I47=0,"",Z47/I47)</f>
+        <f>IF(I47=0,"",(H47+SUM(M47:X47))/I47)</f>
         <v/>
       </c>
       <c r="AC47" s="26" t="n"/>
@@ -3229,15 +3264,15 @@
       <c r="X48" s="21" t="n"/>
       <c r="Y48" s="21" t="n"/>
       <c r="Z48" s="24">
-        <f>SUM(M48:X48)</f>
+        <f>H48+SUM(M48:X48)</f>
         <v/>
       </c>
       <c r="AA48" s="24">
-        <f>I48-Z48</f>
+        <f>I48-H48-SUM(M48:X48)</f>
         <v/>
       </c>
       <c r="AB48" s="25">
-        <f>IF(I48=0,"",Z48/I48)</f>
+        <f>IF(I48=0,"",(H48+SUM(M48:X48))/I48)</f>
         <v/>
       </c>
       <c r="AC48" s="26" t="n"/>
@@ -3278,15 +3313,15 @@
       <c r="X49" s="21" t="n"/>
       <c r="Y49" s="21" t="n"/>
       <c r="Z49" s="24">
-        <f>SUM(M49:X49)</f>
+        <f>H49+SUM(M49:X49)</f>
         <v/>
       </c>
       <c r="AA49" s="24">
-        <f>I49-Z49</f>
+        <f>I49-H49-SUM(M49:X49)</f>
         <v/>
       </c>
       <c r="AB49" s="25">
-        <f>IF(I49=0,"",Z49/I49)</f>
+        <f>IF(I49=0,"",(H49+SUM(M49:X49))/I49)</f>
         <v/>
       </c>
       <c r="AC49" s="26" t="n"/>
@@ -3327,15 +3362,15 @@
       <c r="X50" s="21" t="n"/>
       <c r="Y50" s="21" t="n"/>
       <c r="Z50" s="24">
-        <f>SUM(M50:X50)</f>
+        <f>H50+SUM(M50:X50)</f>
         <v/>
       </c>
       <c r="AA50" s="24">
-        <f>I50-Z50</f>
+        <f>I50-H50-SUM(M50:X50)</f>
         <v/>
       </c>
       <c r="AB50" s="25">
-        <f>IF(I50=0,"",Z50/I50)</f>
+        <f>IF(I50=0,"",(H50+SUM(M50:X50))/I50)</f>
         <v/>
       </c>
       <c r="AC50" s="26" t="n"/>
@@ -3376,15 +3411,15 @@
       <c r="X51" s="21" t="n"/>
       <c r="Y51" s="21" t="n"/>
       <c r="Z51" s="24">
-        <f>SUM(M51:X51)</f>
+        <f>H51+SUM(M51:X51)</f>
         <v/>
       </c>
       <c r="AA51" s="24">
-        <f>I51-Z51</f>
+        <f>I51-H51-SUM(M51:X51)</f>
         <v/>
       </c>
       <c r="AB51" s="25">
-        <f>IF(I51=0,"",Z51/I51)</f>
+        <f>IF(I51=0,"",(H51+SUM(M51:X51))/I51)</f>
         <v/>
       </c>
       <c r="AC51" s="26" t="n"/>
